--- a/toms_raw_data_template.xlsx
+++ b/toms_raw_data_template.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>Reguler (Cashless):18000.00, Instant:18000.00</t>
+          <t>Reguler (Cashless):18000.00, Hemat:18000.00, Agen Shopee:18000.00, Shopee Xpress Point:18000.00, Instant (Versi Lama):18000.00</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">

--- a/toms_raw_data_template.xlsx
+++ b/toms_raw_data_template.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -480,7 +480,6 @@
     <col width="26" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
     <col width="26" customWidth="1" min="30" max="30"/>
-    <col width="26" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -551,90 +550,85 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Stock / Quantity</t>
+          <t>Parent Images</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Parent Images</t>
+          <t>Variant Images (optional)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Variant Images (optional)</t>
+          <t>Weight (kg)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Weight (kg)</t>
+          <t>Length (cm)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Length (cm)</t>
+          <t>Width (cm)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Width (cm)</t>
+          <t>Height (cm)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Height (cm)</t>
+          <t>Specific Category</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Specific Category</t>
+          <t>Gender*</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Gender*</t>
+          <t>Material (optional)</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Material (optional)</t>
+          <t>Shopee Shipping Service</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Shopee Shipping Service</t>
+          <t>Shopee Item Specifications</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Shopee Item Specifications</t>
+          <t>Lazada Item Specifications</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Lazada Item Specifications</t>
+          <t>TikTok Item Specifications</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>TikTok Item Specifications</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Zalora Color</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Zalora Color</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Zalora Images</t>
         </is>
@@ -702,72 +696,71 @@
           <t>Selling price, numbers only.</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Image URLs shared by all variants, separated by ' ; ' (space-semicolon-space). Used for Shopee/Lazada/TikTok.</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Image URLs shared by all variants, separated by ' ; ' (space-semicolon-space). Used for Shopee/Lazada/TikTok.</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
           <t>Image URLs specific to this one variant only, separated by ' ; '. Used for Shopee/Lazada/TikTok — Zalora uses its own separate image field below.</t>
         </is>
       </c>
+      <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>e.g. SNEAKERS, BCKSANDALS, SLIPONS. Used together with the Title keywords for an EXACT match against your Category Mapping file's Specific Category column.</t>
+        </is>
+      </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>e.g. SNEAKERS, BCKSANDALS, SLIPONS. Used together with the Title keywords for an EXACT match against your Category Mapping file's Specific Category column.</t>
+          <t>Code, e.g. WN. Translated into Zalora's own Gender field (WN=Female confirmed so far — more codes to be added as they come up).</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Code, e.g. WN. Translated into Zalora's own Gender field (WN=Female confirmed so far — more codes to be added as they come up).</t>
+          <t>Free text — passed straight into Zalora's Material field as-is (not auto-extracted like Herschel's). Shopee/Lazada's Material spec is always the fixed 'Rubber' regardless of this field.</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Free text — passed straight into Zalora's Material field as-is (not auto-extracted like Herschel's). Shopee/Lazada's Material spec is always the fixed 'Rubber' regardless of this field.</t>
+          <t>Pasted as-is into Shopee's Shipping Service Details column.</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>Pasted as-is into Shopee's Shipping Service Details column.</t>
+          <t>'Key=Value' pairs separated by ' ; ', appended AFTER the automatic Brand=Toms and Material=Rubber entries.</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>'Key=Value' pairs separated by ' ; ', appended AFTER the automatic Brand=Toms and Material=Rubber entries.</t>
+          <t>'Key=Value' pairs separated by ' ; ', appended AFTER the automatic delivery/Hazmat/material entries. Also feeds Lazada's Short Description bullets if that field is left blank.</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>'Key=Value' pairs separated by ' ; ', appended AFTER the automatic delivery/Hazmat/material entries. Also feeds Lazada's Short Description bullets if that field is left blank.</t>
+          <t>'Key=Value' pairs separated by ' ; '. A key matching one of TikTok's named columns (Bahan, Acara, Musim, Bentuk Jari Kaki, Tinggi Hak, Tipe Pengencang, Tipe Hak, Sertifikat SNI) lands directly in that column. Bahan defaults to 'Rubber' and Musim defaults to the Season field below unless overridden here. Unmatched keys are dropped.</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>'Key=Value' pairs separated by ' ; '. A key matching one of TikTok's named columns (Bahan, Acara, Musim, Bentuk Jari Kaki, Tinggi Hak, Tipe Pengencang, Tipe Hak, Sertifikat SNI) lands directly in that column. Bahan defaults to 'Rubber' and Musim defaults to the Season field below unless overridden here. Unmatched keys are dropped.</t>
+          <t>For Zalora's Season column, and TikTok's Musim column (unless overridden in TikTok Item Specifications).</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>For Zalora's Season column, and TikTok's Musim column (unless overridden in TikTok Item Specifications).</t>
+          <t>For Zalora's Year column.</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>For Zalora's Year column.</t>
+          <t>This also drives automatic ColorFamily classification — the tool looks at the first Zalora Image's dominant color first, falling back to matching keywords in this Color name if no image is available.</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>This also drives automatic ColorFamily classification — the tool looks at the first Zalora Image's dominant color first, falling back to matching keywords in this Color name if no image is available.</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>Zalora's own image set (different dimensions than the other 3 marketplaces), separated by ' ; '.</t>
         </is>
@@ -827,45 +820,47 @@
       <c r="M3" s="3" t="n">
         <v>899000</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>https://example.com/img1.jpg ; https://example.com/img2.jpg</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>https://example.com/img1.jpg ; https://example.com/img2.jpg</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>20</v>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>SNEAKERS</t>
+          <t>WN</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>WN</t>
+          <t>Canvas upper, rubber outsole</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>Canvas upper, rubber outsole</t>
+          <t>Reguler (Cashless):18000.00, Hemat:18000.00, Agen Shopee:18000.00, Shopee Xpress Point:18000.00, Instant (Versi Lama):18000.00</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>Reguler (Cashless):18000.00, Hemat:18000.00, Agen Shopee:18000.00, Shopee Xpress Point:18000.00, Instant (Versi Lama):18000.00</t>
+          <t>Toe Style=Round Toe</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -875,28 +870,23 @@
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>Toe Style=Round Toe</t>
+          <t>Bentuk Jari Kaki=Round</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>Bentuk Jari Kaki=Round</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr">
-        <is>
           <t>AUTUMN WINTER</t>
         </is>
       </c>
-      <c r="AC3" s="3" t="n">
+      <c r="AB3" s="3" t="n">
         <v>2026</v>
       </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>Black/White</t>
+        </is>
+      </c>
       <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>Black/White</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>https://example.com/zalora1.jpg ; https://example.com/zalora2.jpg</t>
         </is>
